--- a/collateral/SimReal-投资人邮箱.xlsx
+++ b/collateral/SimReal-投资人邮箱.xlsx
@@ -28148,7 +28148,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>共 135 个邮箱，覆盖 99 家机构或个人：本人公开 42 个，机构投递 / 通用邮箱 93 个。'还没找到'列了其余 650 家：搜过但没有公开邮箱的 100 家，还没搜的 550 家（这一轮搜索额度只够优先的 240 家）。</t>
+          <t>共 135 个邮箱，覆盖 99 家机构或个人：本人公开 42 个，机构投递 / 通用邮箱 93 个。'还没找到'列了其余 650 家：搜过但没有公开邮箱的 100 家，还没搜的 550 家（这一轮的搜索额度只够排在前面的 172 家）。</t>
         </is>
       </c>
     </row>
